--- a/迈克尔逊干涉仪.xlsx
+++ b/迈克尔逊干涉仪.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Repos\fuck-UPE\大物实验\数据处理-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Repos\fuck-UPE\大物实验\数据处理-保护branch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A11EAF-4D0A-40A9-857F-DB8F804CF0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E03DE6-DA57-42AB-8B79-B6266337C4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1772,6 +1772,7 @@
       <c r="A23" s="8"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
